--- a/data/templates/pcs_fap_tension_template.xlsx
+++ b/data/templates/pcs_fap_tension_template.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -386,12 +386,19 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>La tension est celle de la FAP en France entière : jamais une tension du département.</t>
+          <t>Depuis l édition 2023 de la Dares, le niveau 5 est affiné en 5.1 et 5.2 (5.2 la plus forte) : TENSION_SOUS_NIVEAUX.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>La tension est celle de la FAP en France entière : jamais une tension du département.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Déposer le vrai classeur sous data/pcs_fap_tension.xlsx (non versionné).</t>
         </is>
@@ -404,7 +411,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -470,7 +477,7 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>ind_condition_travail_d</t>
+          <t>ind_cond_travail_d</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -480,12 +487,12 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>ind_inacttract_salariale_d</t>
+          <t>ind_inattract_salariale_d</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>ind_specif_form_emploi_d</t>
+          <t>ind_specif_form_empl_d</t>
         </is>
       </c>
     </row>
@@ -523,13 +530,13 @@
         <v>10</v>
       </c>
       <c r="I2">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="J2">
         <v>3</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -581,7 +588,7 @@
         <v>5</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J3">
         <v>3</v>
@@ -593,7 +600,7 @@
         <v>2</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="N3">
         <v>1</v>
@@ -719,6 +726,64 @@
       </c>
       <c r="P5">
         <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>X05E</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Métier fictif 5</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>F4Z04</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Famille fictive 4</t>
+        </is>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>300</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>2</v>
+      </c>
+      <c r="P6">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
